--- a/data/trans_orig/P2B_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35743</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58164</t>
+          <t>58817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56459</t>
+          <t>59467</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86632</t>
+          <t>87988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99658</t>
+          <t>100820</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136860</t>
+          <t>136384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133614</t>
+          <t>132961</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156035</t>
+          <t>156305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112381</t>
+          <t>111025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142554</t>
+          <t>139546</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253931</t>
+          <t>254407</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291133</t>
+          <t>289971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55619</t>
+          <t>56557</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87751</t>
+          <t>87078</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90668</t>
+          <t>89997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125596</t>
+          <t>125343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156264</t>
+          <t>156490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203186</t>
+          <t>201932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>286189</t>
+          <t>286862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>318321</t>
+          <t>317383</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>319333</t>
+          <t>319586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354261</t>
+          <t>354932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>615683</t>
+          <t>616937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>662605</t>
+          <t>662379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33276</t>
+          <t>34674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58719</t>
+          <t>58770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75728</t>
+          <t>74758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107034</t>
+          <t>105872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115833</t>
+          <t>117190</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155093</t>
+          <t>155546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181870</t>
+          <t>181819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>207313</t>
+          <t>205915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178957</t>
+          <t>180119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210263</t>
+          <t>211233</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371487</t>
+          <t>371034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>410747</t>
+          <t>409390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27901</t>
+          <t>27993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50762</t>
+          <t>51467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59805</t>
+          <t>60920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89631</t>
+          <t>89816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96345</t>
+          <t>95502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133196</t>
+          <t>132639</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215923</t>
+          <t>215218</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>238784</t>
+          <t>238692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>232070</t>
+          <t>231885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261896</t>
+          <t>260781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>455190</t>
+          <t>455747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>492041</t>
+          <t>492884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>30437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53469</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>32805</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57785</t>
+          <t>57468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72520</t>
+          <t>71824</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104419</t>
+          <t>104050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98312</t>
+          <t>99775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119915</t>
+          <t>121344</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129378</t>
+          <t>129695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152224</t>
+          <t>154358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234525</t>
+          <t>234894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266424</t>
+          <t>267120</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44572</t>
+          <t>43792</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37408</t>
+          <t>36259</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59952</t>
+          <t>60656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64941</t>
+          <t>64755</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95910</t>
+          <t>96435</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169645</t>
+          <t>170425</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>166550</t>
+          <t>165846</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189094</t>
+          <t>190243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>344809</t>
+          <t>344284</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>375778</t>
+          <t>375964</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73017</t>
+          <t>71789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105414</t>
+          <t>105352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119754</t>
+          <t>121428</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160311</t>
+          <t>159561</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>202169</t>
+          <t>203307</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>258871</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>335631</t>
+          <t>335693</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>368028</t>
+          <t>369256</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>378261</t>
+          <t>379011</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>418818</t>
+          <t>417144</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>723735</t>
+          <t>720746</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>777448</t>
+          <t>776310</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>154255</t>
+          <t>152931</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>199917</t>
+          <t>199317</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152034</t>
+          <t>151235</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>199006</t>
+          <t>197550</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>317622</t>
+          <t>321164</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>382156</t>
+          <t>384120</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>384532</t>
+          <t>385132</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>430194</t>
+          <t>431518</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>470575</t>
+          <t>472031</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>517547</t>
+          <t>518346</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>871874</t>
+          <t>869910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>936408</t>
+          <t>932866</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>498707</t>
+          <t>498664</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>579750</t>
+          <t>585848</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>710346</t>
+          <t>705160</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>800129</t>
+          <t>801015</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1229084</t>
+          <t>1231143</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1358587</t>
+          <t>1358193</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1884733</t>
+          <t>1878635</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1965776</t>
+          <t>1965819</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2073324</t>
+          <t>2072438</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2163107</t>
+          <t>2168293</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3979349</t>
+          <t>3979743</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4108852</t>
+          <t>4106793</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122319</t>
+          <t>123083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154912</t>
+          <t>153746</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141055</t>
+          <t>143060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>176748</t>
+          <t>177266</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>275467</t>
+          <t>277556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>322295</t>
+          <t>322351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,82%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80340</t>
+          <t>81506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112933</t>
+          <t>112169</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93093</t>
+          <t>92575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128786</t>
+          <t>126781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>182798</t>
+          <t>182742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229626</t>
+          <t>227537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170105</t>
+          <t>170982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>213880</t>
+          <t>212326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>223069</t>
+          <t>222969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>267637</t>
+          <t>266864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>405403</t>
+          <t>406381</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>466563</t>
+          <t>464829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184088</t>
+          <t>185642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227863</t>
+          <t>226986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193580</t>
+          <t>194353</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238148</t>
+          <t>238248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>392621</t>
+          <t>394355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>453781</t>
+          <t>452803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112054</t>
+          <t>112182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144363</t>
+          <t>144947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>145762</t>
+          <t>145123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180273</t>
+          <t>180432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>267071</t>
+          <t>265413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314783</t>
+          <t>316109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,19%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120994</t>
+          <t>120410</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153303</t>
+          <t>153175</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116921</t>
+          <t>116762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151432</t>
+          <t>152071</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>247768</t>
+          <t>246442</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295480</t>
+          <t>297138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162729</t>
+          <t>161717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200998</t>
+          <t>199949</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201921</t>
+          <t>198212</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238362</t>
+          <t>238385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>376084</t>
+          <t>376949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>426511</t>
+          <t>426759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113236</t>
+          <t>114285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151505</t>
+          <t>152517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113579</t>
+          <t>113556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>150020</t>
+          <t>153729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239665</t>
+          <t>239417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290092</t>
+          <t>289227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80240</t>
+          <t>80244</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107831</t>
+          <t>107448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97247</t>
+          <t>98255</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125748</t>
+          <t>126016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>184110</t>
+          <t>185513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225062</t>
+          <t>224796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67724</t>
+          <t>68107</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95315</t>
+          <t>95311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77319</t>
+          <t>77051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105820</t>
+          <t>104812</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153560</t>
+          <t>153826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194512</t>
+          <t>193109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107000</t>
+          <t>104617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>137052</t>
+          <t>136661</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105071</t>
+          <t>106287</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>136833</t>
+          <t>136967</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>219456</t>
+          <t>219574</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>263776</t>
+          <t>263354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93283</t>
+          <t>93674</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123335</t>
+          <t>125718</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>118652</t>
+          <t>118518</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150414</t>
+          <t>149198</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>222044</t>
+          <t>222466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>266364</t>
+          <t>266246</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>226077</t>
+          <t>227721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>277676</t>
+          <t>275372</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>263575</t>
+          <t>263708</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>315238</t>
+          <t>314327</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>506342</t>
+          <t>508508</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>571162</t>
+          <t>577535</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246149</t>
+          <t>248453</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>297748</t>
+          <t>296104</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>288419</t>
+          <t>289330</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>340082</t>
+          <t>339949</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>556320</t>
+          <t>549947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>621140</t>
+          <t>618974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>289522</t>
+          <t>292053</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>341509</t>
+          <t>342547</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>364422</t>
+          <t>364172</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>418428</t>
+          <t>420569</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>672019</t>
+          <t>674066</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>745423</t>
+          <t>749433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>264187</t>
+          <t>263149</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>316174</t>
+          <t>313643</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>282750</t>
+          <t>280609</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>336756</t>
+          <t>337006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>561451</t>
+          <t>557441</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>634855</t>
+          <t>632808</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1368979</t>
+          <t>1366860</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1478154</t>
+          <t>1474978</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1645976</t>
+          <t>1642075</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1756874</t>
+          <t>1759869</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3045590</t>
+          <t>3046118</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3212455</t>
+          <t>3207681</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1270068</t>
+          <t>1273244</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1379243</t>
+          <t>1381362</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1386707</t>
+          <t>1383712</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1497605</t>
+          <t>1501506</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2679348</t>
+          <t>2684122</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2846213</t>
+          <t>2845685</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89673</t>
+          <t>87748</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122316</t>
+          <t>119565</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110243</t>
+          <t>110621</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>143174</t>
+          <t>142772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207906</t>
+          <t>208579</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253115</t>
+          <t>254504</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105011</t>
+          <t>107762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137654</t>
+          <t>139579</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107233</t>
+          <t>107635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140164</t>
+          <t>139786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224620</t>
+          <t>223231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>269829</t>
+          <t>269156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59055</t>
+          <t>60643</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91859</t>
+          <t>91485</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88532</t>
+          <t>87888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125643</t>
+          <t>123334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>160386</t>
+          <t>155688</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205320</t>
+          <t>203634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>291336</t>
+          <t>291710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>324140</t>
+          <t>322552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322684</t>
+          <t>324993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359795</t>
+          <t>360439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>626202</t>
+          <t>627888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>671136</t>
+          <t>675834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46478</t>
+          <t>47473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71181</t>
+          <t>71938</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66948</t>
+          <t>68179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96496</t>
+          <t>97357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122010</t>
+          <t>121461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161236</t>
+          <t>162404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164776</t>
+          <t>164019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>189479</t>
+          <t>188484</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172359</t>
+          <t>171498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>201907</t>
+          <t>200676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>343576</t>
+          <t>342408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>382802</t>
+          <t>383351</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94377</t>
+          <t>94756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127916</t>
+          <t>126422</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143376</t>
+          <t>140709</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180231</t>
+          <t>179310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>247063</t>
+          <t>244170</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>299229</t>
+          <t>295131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143931</t>
+          <t>145425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177470</t>
+          <t>177091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160426</t>
+          <t>161347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197281</t>
+          <t>199948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>313275</t>
+          <t>317373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>365441</t>
+          <t>368334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,14%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89835</t>
+          <t>90781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115364</t>
+          <t>114925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>107675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132436</t>
+          <t>133578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>203876</t>
+          <t>205119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>240674</t>
+          <t>241267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,23%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57285</t>
+          <t>57724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82814</t>
+          <t>81868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53789</t>
+          <t>52647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78525</t>
+          <t>78550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118200</t>
+          <t>117607</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154998</t>
+          <t>153755</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69713</t>
+          <t>69202</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97232</t>
+          <t>95112</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79566</t>
+          <t>80347</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109066</t>
+          <t>110412</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>154863</t>
+          <t>158058</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>194888</t>
+          <t>196193</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,49%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96621</t>
+          <t>98741</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124140</t>
+          <t>124651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101657</t>
+          <t>100311</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131157</t>
+          <t>130376</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>209688</t>
+          <t>208383</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>249713</t>
+          <t>246518</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>134153</t>
+          <t>136207</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179116</t>
+          <t>178958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>221318</t>
+          <t>222283</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>271313</t>
+          <t>271583</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>373461</t>
+          <t>372323</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>437256</t>
+          <t>437270</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258950</t>
+          <t>259108</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>303913</t>
+          <t>301859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>282757</t>
+          <t>282487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>332752</t>
+          <t>331787</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>554880</t>
+          <t>554866</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>618675</t>
+          <t>619813</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>325557</t>
+          <t>322634</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>370491</t>
+          <t>370107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>426095</t>
+          <t>422707</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>478516</t>
+          <t>477882</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>763343</t>
+          <t>760352</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>834205</t>
+          <t>835157</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>205608</t>
+          <t>205992</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>250542</t>
+          <t>253465</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>215343</t>
+          <t>215977</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>267764</t>
+          <t>271152</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>435753</t>
+          <t>434801</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>506615</t>
+          <t>509606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>987571</t>
+          <t>992738</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1086042</t>
+          <t>1089928</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1331846</t>
+          <t>1332406</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1444516</t>
+          <t>1446870</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2350037</t>
+          <t>2355148</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2502291</t>
+          <t>2502314</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1412951</t>
+          <t>1409065</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1511422</t>
+          <t>1506255</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1508607</t>
+          <t>1506253</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1621277</t>
+          <t>1620717</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2949825</t>
+          <t>2949802</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3102079</t>
+          <t>3096968</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023</t>
+          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23493</t>
+          <t>23933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39611</t>
+          <t>40874</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>44687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69321</t>
+          <t>68884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216503</t>
+          <t>215839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>234212</t>
+          <t>235156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>211509</t>
+          <t>210246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227627</t>
+          <t>227187</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>433186</t>
+          <t>433623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>458331</t>
+          <t>457820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52867</t>
+          <t>54295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87861</t>
+          <t>87486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97225</t>
+          <t>98065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>129549</t>
+          <t>131415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161925</t>
+          <t>160616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208261</t>
+          <t>207173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250431</t>
+          <t>250806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>285425</t>
+          <t>283997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>285088</t>
+          <t>283222</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317412</t>
+          <t>316572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>544667</t>
+          <t>545755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>591003</t>
+          <t>592312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,67%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33318</t>
+          <t>33831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54472</t>
+          <t>55433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51328</t>
+          <t>52115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74823</t>
+          <t>73575</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89266</t>
+          <t>88606</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122026</t>
+          <t>120077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172559</t>
+          <t>171598</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193713</t>
+          <t>193200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191834</t>
+          <t>193082</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>215329</t>
+          <t>214542</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371663</t>
+          <t>373612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>404423</t>
+          <t>405083</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>45101</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74316</t>
+          <t>74258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43539</t>
+          <t>40801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103678</t>
+          <t>105358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91095</t>
+          <t>84956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167363</t>
+          <t>165343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136435</t>
+          <t>136493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165809</t>
+          <t>165650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>287249</t>
+          <t>285569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>347388</t>
+          <t>350126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>434315</t>
+          <t>436335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>510583</t>
+          <t>516722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29779</t>
+          <t>30471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44580</t>
+          <t>45687</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68305</t>
+          <t>69126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>65956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80370</t>
+          <t>80240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144257</t>
+          <t>143150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175354</t>
+          <t>174632</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216959</t>
+          <t>216138</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>254323</t>
+          <t>254790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46867</t>
+          <t>46812</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69542</t>
+          <t>69323</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61025</t>
+          <t>61288</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80880</t>
+          <t>82190</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114451</t>
+          <t>113642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144068</t>
+          <t>144340</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134062</t>
+          <t>134281</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156737</t>
+          <t>156792</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126994</t>
+          <t>125684</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>146849</t>
+          <t>146586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>267410</t>
+          <t>267138</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>297027</t>
+          <t>297836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,38%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35171</t>
+          <t>35503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64012</t>
+          <t>65774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82912</t>
+          <t>84561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>490499</t>
+          <t>493758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>131054</t>
+          <t>130415</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>694171</t>
+          <t>676363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>347995</t>
+          <t>346233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>376836</t>
+          <t>376504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>184191</t>
+          <t>180932</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>591778</t>
+          <t>590129</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>392526</t>
+          <t>410334</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>955643</t>
+          <t>956282</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>150836</t>
+          <t>154359</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>190175</t>
+          <t>191356</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>234017</t>
+          <t>236019</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>275031</t>
+          <t>274828</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>396110</t>
+          <t>398780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>450983</t>
+          <t>452542</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>239714</t>
+          <t>238533</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>279053</t>
+          <t>275530</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>263938</t>
+          <t>264141</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>304952</t>
+          <t>302950</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>517875</t>
+          <t>516316</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>572748</t>
+          <t>570078</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>458338</t>
+          <t>456947</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>541364</t>
+          <t>536612</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>733652</t>
+          <t>735655</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1372674</t>
+          <t>1404661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1224278</t>
+          <t>1219515</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1953711</t>
+          <t>1961677</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1628023</t>
+          <t>1632775</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1711049</t>
+          <t>1712440</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1561038</t>
+          <t>1529051</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2200060</t>
+          <t>2198057</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3149388</t>
+          <t>3141422</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3878821</t>
+          <t>3883584</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2B_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35473</t>
+          <t>34619</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58817</t>
+          <t>58746</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59467</t>
+          <t>57865</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87988</t>
+          <t>86224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100820</t>
+          <t>100906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136384</t>
+          <t>136691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132961</t>
+          <t>133032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156305</t>
+          <t>157159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111025</t>
+          <t>112789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139546</t>
+          <t>141148</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254407</t>
+          <t>254100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>289971</t>
+          <t>289885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,18%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56557</t>
+          <t>55957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87078</t>
+          <t>86916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89997</t>
+          <t>90766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125343</t>
+          <t>124686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156490</t>
+          <t>156836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>201932</t>
+          <t>204302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>286862</t>
+          <t>287024</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>317383</t>
+          <t>317983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>319586</t>
+          <t>320243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354932</t>
+          <t>354163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>616937</t>
+          <t>614567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>662379</t>
+          <t>662033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34674</t>
+          <t>33970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58770</t>
+          <t>58214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74758</t>
+          <t>75370</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105872</t>
+          <t>105736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117190</t>
+          <t>116338</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155546</t>
+          <t>155915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181819</t>
+          <t>182375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205915</t>
+          <t>206619</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180119</t>
+          <t>180255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>211233</t>
+          <t>210621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371034</t>
+          <t>370665</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>409390</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27993</t>
+          <t>27527</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51467</t>
+          <t>49717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60920</t>
+          <t>61893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89816</t>
+          <t>91518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95502</t>
+          <t>94285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132639</t>
+          <t>132999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215218</t>
+          <t>216968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>238692</t>
+          <t>239158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231885</t>
+          <t>230183</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>260781</t>
+          <t>259808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>455747</t>
+          <t>455387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>492884</t>
+          <t>494101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30437</t>
+          <t>30849</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>53697</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57468</t>
+          <t>57947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71824</t>
+          <t>71861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104050</t>
+          <t>103671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99775</t>
+          <t>98084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121344</t>
+          <t>120932</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129695</t>
+          <t>129216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154358</t>
+          <t>153092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234894</t>
+          <t>235273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267120</t>
+          <t>267083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>23066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43792</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36259</t>
+          <t>36702</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60656</t>
+          <t>60606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64755</t>
+          <t>64829</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96435</t>
+          <t>96597</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170425</t>
+          <t>170881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191265</t>
+          <t>191151</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>165846</t>
+          <t>165896</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>190243</t>
+          <t>189800</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>344284</t>
+          <t>344122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>375964</t>
+          <t>375890</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71789</t>
+          <t>70662</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105352</t>
+          <t>109623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121428</t>
+          <t>119039</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>159561</t>
+          <t>160428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>203307</t>
+          <t>204436</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>258871</t>
+          <t>256717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>335693</t>
+          <t>331422</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>369256</t>
+          <t>370383</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>379011</t>
+          <t>378144</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>417144</t>
+          <t>419533</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>720746</t>
+          <t>722900</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>776310</t>
+          <t>775181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>152931</t>
+          <t>151849</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>199317</t>
+          <t>196233</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>151235</t>
+          <t>150501</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>197550</t>
+          <t>195717</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>321164</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>384120</t>
+          <t>383960</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>385132</t>
+          <t>388216</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>431518</t>
+          <t>432600</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>472031</t>
+          <t>473864</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>518346</t>
+          <t>519080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>869910</t>
+          <t>870070</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>932866</t>
+          <t>936279</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,66%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>498664</t>
+          <t>494437</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>585848</t>
+          <t>581117</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>705160</t>
+          <t>705373</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>801015</t>
+          <t>797847</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1231143</t>
+          <t>1230628</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1358193</t>
+          <t>1358434</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1878635</t>
+          <t>1883366</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1965819</t>
+          <t>1970046</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2072438</t>
+          <t>2075606</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2168293</t>
+          <t>2168080</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3979743</t>
+          <t>3979502</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4106793</t>
+          <t>4107308</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123083</t>
+          <t>122634</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153746</t>
+          <t>154506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143060</t>
+          <t>143599</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177266</t>
+          <t>178104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>277556</t>
+          <t>277379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>322351</t>
+          <t>321143</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81506</t>
+          <t>80746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112169</t>
+          <t>112618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92575</t>
+          <t>91737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126781</t>
+          <t>126242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>182742</t>
+          <t>183950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227537</t>
+          <t>227714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170982</t>
+          <t>171202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>212326</t>
+          <t>212885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>222969</t>
+          <t>221836</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>266864</t>
+          <t>267048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>406381</t>
+          <t>402926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>464829</t>
+          <t>467734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185642</t>
+          <t>185083</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226986</t>
+          <t>226766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194353</t>
+          <t>194169</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238248</t>
+          <t>239381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>394355</t>
+          <t>391450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>452803</t>
+          <t>456258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112182</t>
+          <t>113433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144947</t>
+          <t>144568</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>145123</t>
+          <t>144997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180432</t>
+          <t>180652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>265413</t>
+          <t>265884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>316109</t>
+          <t>314110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,84%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120410</t>
+          <t>120789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153175</t>
+          <t>151924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116762</t>
+          <t>116542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152071</t>
+          <t>152197</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246442</t>
+          <t>248441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297138</t>
+          <t>296667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>161717</t>
+          <t>164607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199949</t>
+          <t>198764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>198212</t>
+          <t>200824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238385</t>
+          <t>237383</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>376949</t>
+          <t>374793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>426759</t>
+          <t>428235</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,28%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114285</t>
+          <t>115470</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152517</t>
+          <t>149627</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113556</t>
+          <t>114558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153729</t>
+          <t>151117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239417</t>
+          <t>237941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>289227</t>
+          <t>291383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80244</t>
+          <t>78962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107448</t>
+          <t>106537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98255</t>
+          <t>98022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126016</t>
+          <t>127753</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185513</t>
+          <t>186551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224796</t>
+          <t>226169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,73%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68107</t>
+          <t>69018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95311</t>
+          <t>96593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77051</t>
+          <t>75314</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104812</t>
+          <t>105045</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153826</t>
+          <t>152453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>193109</t>
+          <t>192071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104617</t>
+          <t>106123</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>136661</t>
+          <t>138105</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106287</t>
+          <t>105845</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>136967</t>
+          <t>136328</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>219574</t>
+          <t>221068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>263354</t>
+          <t>265041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93674</t>
+          <t>92230</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125718</t>
+          <t>124212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>118518</t>
+          <t>119157</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>149198</t>
+          <t>149640</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>222466</t>
+          <t>220779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>266246</t>
+          <t>264752</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>227721</t>
+          <t>227186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>275372</t>
+          <t>275377</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>263708</t>
+          <t>263599</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314327</t>
+          <t>312666</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>508508</t>
+          <t>503226</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>577535</t>
+          <t>570972</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>248453</t>
+          <t>248448</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>296104</t>
+          <t>296639</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>289330</t>
+          <t>290991</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>339949</t>
+          <t>340058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>549947</t>
+          <t>556510</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>618974</t>
+          <t>624256</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>292053</t>
+          <t>292553</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>342547</t>
+          <t>343798</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>364172</t>
+          <t>362795</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>420569</t>
+          <t>418069</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>674066</t>
+          <t>671942</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>749433</t>
+          <t>747811</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>263149</t>
+          <t>261898</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>313643</t>
+          <t>313143</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>280609</t>
+          <t>283109</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>337006</t>
+          <t>338383</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>557441</t>
+          <t>559063</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>632808</t>
+          <t>634932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,58%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1366860</t>
+          <t>1366682</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1474978</t>
+          <t>1477050</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1642075</t>
+          <t>1646138</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1759869</t>
+          <t>1755358</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3046118</t>
+          <t>3038954</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3207681</t>
+          <t>3202251</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1273244</t>
+          <t>1271172</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1381362</t>
+          <t>1381540</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1383712</t>
+          <t>1388223</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1501506</t>
+          <t>1497443</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2684122</t>
+          <t>2689552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2845685</t>
+          <t>2852849</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87748</t>
+          <t>90846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119565</t>
+          <t>119752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110621</t>
+          <t>111964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>142772</t>
+          <t>144359</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208579</t>
+          <t>207208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254504</t>
+          <t>253713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,11%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107762</t>
+          <t>107575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>139579</t>
+          <t>136481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107635</t>
+          <t>106048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139786</t>
+          <t>138443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>223231</t>
+          <t>224022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>269156</t>
+          <t>270527</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60643</t>
+          <t>60688</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91485</t>
+          <t>91837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87888</t>
+          <t>88902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123334</t>
+          <t>125454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155688</t>
+          <t>155580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203634</t>
+          <t>207095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>291710</t>
+          <t>291358</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322552</t>
+          <t>322507</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324993</t>
+          <t>322873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360439</t>
+          <t>359425</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>627888</t>
+          <t>624427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>675834</t>
+          <t>675942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47473</t>
+          <t>47558</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71938</t>
+          <t>72502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68179</t>
+          <t>65822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97357</t>
+          <t>96529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121461</t>
+          <t>119111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162404</t>
+          <t>160027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164019</t>
+          <t>163455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188484</t>
+          <t>188399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171498</t>
+          <t>172326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200676</t>
+          <t>203033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342408</t>
+          <t>344785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>383351</t>
+          <t>385701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94756</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126422</t>
+          <t>126802</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>140709</t>
+          <t>140306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>179310</t>
+          <t>179025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244170</t>
+          <t>243846</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295131</t>
+          <t>295537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145425</t>
+          <t>145045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177091</t>
+          <t>178401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161347</t>
+          <t>161632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>199948</t>
+          <t>200351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>317373</t>
+          <t>316967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>368334</t>
+          <t>368658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90781</t>
+          <t>89918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114925</t>
+          <t>115036</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107675</t>
+          <t>107744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133578</t>
+          <t>132708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>205119</t>
+          <t>204820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>241267</t>
+          <t>240396</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57724</t>
+          <t>57613</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81868</t>
+          <t>82731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52647</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78550</t>
+          <t>78481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117607</t>
+          <t>118478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153755</t>
+          <t>154054</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69202</t>
+          <t>68477</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95112</t>
+          <t>95801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80347</t>
+          <t>78937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110412</t>
+          <t>109794</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158058</t>
+          <t>154336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>196193</t>
+          <t>195325</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98741</t>
+          <t>98052</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124651</t>
+          <t>125376</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>100311</t>
+          <t>100929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>130376</t>
+          <t>131786</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>208383</t>
+          <t>209251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>246518</t>
+          <t>250240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,85%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136207</t>
+          <t>137578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178958</t>
+          <t>179374</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>222283</t>
+          <t>221984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>271583</t>
+          <t>270891</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>372323</t>
+          <t>374750</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>437270</t>
+          <t>440291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>259108</t>
+          <t>258692</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>301859</t>
+          <t>300488</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>282487</t>
+          <t>283179</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>331787</t>
+          <t>332086</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>554866</t>
+          <t>551845</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>619813</t>
+          <t>617386</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>322634</t>
+          <t>322913</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>370107</t>
+          <t>370685</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>422707</t>
+          <t>425472</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>477882</t>
+          <t>479528</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>760352</t>
+          <t>763019</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>835157</t>
+          <t>835449</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,79%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>205992</t>
+          <t>205414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>253465</t>
+          <t>253186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>215977</t>
+          <t>214331</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>271152</t>
+          <t>268387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>434801</t>
+          <t>434509</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>509606</t>
+          <t>506939</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>992738</t>
+          <t>989298</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1089928</t>
+          <t>1093685</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1332406</t>
+          <t>1329864</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1446870</t>
+          <t>1438320</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2355148</t>
+          <t>2346271</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2502314</t>
+          <t>2495542</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1409065</t>
+          <t>1405308</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1506255</t>
+          <t>1509695</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1506253</t>
+          <t>1514803</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1620717</t>
+          <t>1623259</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2949802</t>
+          <t>2956574</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3096968</t>
+          <t>3105845</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>35249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30907</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23933</t>
+          <t>26940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40874</t>
+          <t>43578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>55837</t>
+          <t>60348</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44687</t>
+          <t>48893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68884</t>
+          <t>73044</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>226458</t>
+          <t>222667</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215839</t>
+          <t>212778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>235156</t>
+          <t>229685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>220213</t>
+          <t>235493</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210246</t>
+          <t>226903</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227187</t>
+          <t>243541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>446670</t>
+          <t>458160</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>433623</t>
+          <t>445464</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>457820</t>
+          <t>469615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>251387</t>
+          <t>248027</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>251387</t>
+          <t>248027</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>251387</t>
+          <t>248027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>251120</t>
+          <t>270481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>251120</t>
+          <t>270481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>251120</t>
+          <t>270481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>502507</t>
+          <t>518508</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>502507</t>
+          <t>518508</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>502507</t>
+          <t>518508</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>76819</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54295</t>
+          <t>59970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87486</t>
+          <t>96307</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>112490</t>
+          <t>124692</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98065</t>
+          <t>107728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131415</t>
+          <t>140110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>182173</t>
+          <t>201511</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>160616</t>
+          <t>177978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207173</t>
+          <t>225451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>268609</t>
+          <t>274903</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250806</t>
+          <t>255415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>283997</t>
+          <t>291752</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>302147</t>
+          <t>317339</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>283222</t>
+          <t>301921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316572</t>
+          <t>334303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>570755</t>
+          <t>592242</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>545755</t>
+          <t>568302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>592312</t>
+          <t>615775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>77,58%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>338292</t>
+          <t>351722</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>338292</t>
+          <t>351722</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>338292</t>
+          <t>351722</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>414637</t>
+          <t>442031</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>414637</t>
+          <t>442031</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>414637</t>
+          <t>442031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>752928</t>
+          <t>793753</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>752928</t>
+          <t>793753</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>752928</t>
+          <t>793753</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>44544</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>35798</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55433</t>
+          <t>57558</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61323</t>
+          <t>60902</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52115</t>
+          <t>50633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73575</t>
+          <t>72891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>104727</t>
+          <t>105447</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88606</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120077</t>
+          <t>120292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>183627</t>
+          <t>183088</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171598</t>
+          <t>170074</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193200</t>
+          <t>191834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>205334</t>
+          <t>213305</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193082</t>
+          <t>201316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>214542</t>
+          <t>223574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>388962</t>
+          <t>396392</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373612</t>
+          <t>381547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>405083</t>
+          <t>411953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>227031</t>
+          <t>227632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>227031</t>
+          <t>227632</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227031</t>
+          <t>227632</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>266657</t>
+          <t>274207</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>266657</t>
+          <t>274207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>266657</t>
+          <t>274207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>493689</t>
+          <t>501839</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>493689</t>
+          <t>501839</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>493689</t>
+          <t>501839</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58802</t>
+          <t>71894</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45101</t>
+          <t>56281</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74258</t>
+          <t>91146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>76294</t>
+          <t>86567</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40801</t>
+          <t>72756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105358</t>
+          <t>101401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>135096</t>
+          <t>158461</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84956</t>
+          <t>135145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165343</t>
+          <t>181773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>151949</t>
+          <t>179373</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136493</t>
+          <t>160121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165650</t>
+          <t>194986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>314633</t>
+          <t>241846</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>285569</t>
+          <t>227012</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>350126</t>
+          <t>255657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>466582</t>
+          <t>421219</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>436335</t>
+          <t>397907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>516722</t>
+          <t>444535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>210751</t>
+          <t>251267</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>210751</t>
+          <t>251267</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>210751</t>
+          <t>251267</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>390927</t>
+          <t>328413</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>390927</t>
+          <t>328413</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>390927</t>
+          <t>328413</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>601678</t>
+          <t>579680</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>601678</t>
+          <t>579680</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>601678</t>
+          <t>579680</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>26399</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>19310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>35745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>27948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45687</t>
+          <t>43145</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>53417</t>
+          <t>60791</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30474</t>
+          <t>51279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69126</t>
+          <t>71442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74044</t>
+          <t>82716</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65956</t>
+          <t>73370</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80240</t>
+          <t>89805</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>157803</t>
+          <t>119110</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143150</t>
+          <t>110357</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174632</t>
+          <t>125554</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>231847</t>
+          <t>201825</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216138</t>
+          <t>191174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>254790</t>
+          <t>211337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96427</t>
+          <t>109115</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96427</t>
+          <t>109115</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96427</t>
+          <t>109115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>188837</t>
+          <t>153502</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>188837</t>
+          <t>153502</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>188837</t>
+          <t>153502</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>285264</t>
+          <t>262616</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>285264</t>
+          <t>262616</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>285264</t>
+          <t>262616</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57830</t>
+          <t>60259</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46812</t>
+          <t>51052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69323</t>
+          <t>72943</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70800</t>
+          <t>72627</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61288</t>
+          <t>61993</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82190</t>
+          <t>82729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>128630</t>
+          <t>132886</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113642</t>
+          <t>118100</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144340</t>
+          <t>148701</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>145774</t>
+          <t>144230</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134281</t>
+          <t>131546</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>153437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>137074</t>
+          <t>141306</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125684</t>
+          <t>131204</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>146586</t>
+          <t>151940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>282848</t>
+          <t>285536</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>267138</t>
+          <t>269721</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>297836</t>
+          <t>300322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>203604</t>
+          <t>204489</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>203604</t>
+          <t>204489</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>203604</t>
+          <t>204489</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>207874</t>
+          <t>213933</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>207874</t>
+          <t>213933</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>207874</t>
+          <t>213933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>411478</t>
+          <t>418422</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>411478</t>
+          <t>418422</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>411478</t>
+          <t>418422</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>48547</t>
+          <t>59456</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35503</t>
+          <t>44771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65774</t>
+          <t>76723</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>266994</t>
+          <t>82679</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84561</t>
+          <t>69162</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>493758</t>
+          <t>98667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>315542</t>
+          <t>142135</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130415</t>
+          <t>123394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>676363</t>
+          <t>166203</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>363460</t>
+          <t>426309</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>346233</t>
+          <t>409042</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>376504</t>
+          <t>440994</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>407696</t>
+          <t>495250</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180932</t>
+          <t>479262</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>590129</t>
+          <t>508767</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>771155</t>
+          <t>921559</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>410334</t>
+          <t>897491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>956282</t>
+          <t>940300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>412007</t>
+          <t>485765</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>412007</t>
+          <t>485765</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>412007</t>
+          <t>485765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>674690</t>
+          <t>577929</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>674690</t>
+          <t>577929</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>674690</t>
+          <t>577929</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1086697</t>
+          <t>1063694</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1086697</t>
+          <t>1063694</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1086697</t>
+          <t>1063694</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>170592</t>
+          <t>206518</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>154359</t>
+          <t>184722</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>191356</t>
+          <t>229534</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>255117</t>
+          <t>301683</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>236019</t>
+          <t>280688</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>274828</t>
+          <t>326579</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>425709</t>
+          <t>508202</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>398780</t>
+          <t>476010</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>452542</t>
+          <t>540199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>259297</t>
+          <t>290906</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>238533</t>
+          <t>267890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275530</t>
+          <t>312702</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>283852</t>
+          <t>319172</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>264141</t>
+          <t>294276</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>302950</t>
+          <t>340167</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>543149</t>
+          <t>610078</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>516316</t>
+          <t>578081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>570078</t>
+          <t>642270</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>429889</t>
+          <t>497424</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>429889</t>
+          <t>497424</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>429889</t>
+          <t>497424</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>538969</t>
+          <t>620855</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>538969</t>
+          <t>620855</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>538969</t>
+          <t>620855</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>968858</t>
+          <t>1118280</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>968858</t>
+          <t>1118280</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>968858</t>
+          <t>1118280</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>496170</t>
+          <t>571250</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>456947</t>
+          <t>526661</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>536612</t>
+          <t>616392</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>904961</t>
+          <t>798531</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>735655</t>
+          <t>761055</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1404661</t>
+          <t>840593</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1401131</t>
+          <t>1369781</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1219515</t>
+          <t>1311410</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1961677</t>
+          <t>1430828</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1673217</t>
+          <t>1804190</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1632775</t>
+          <t>1759048</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1712440</t>
+          <t>1848779</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2028751</t>
+          <t>2082821</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1529051</t>
+          <t>2040759</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2198057</t>
+          <t>2120297</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3701968</t>
+          <t>3887011</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3141422</t>
+          <t>3825964</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3883584</t>
+          <t>3945382</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2169387</t>
+          <t>2375440</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2169387</t>
+          <t>2375440</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2169387</t>
+          <t>2375440</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2933712</t>
+          <t>2881352</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2933712</t>
+          <t>2881352</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2933712</t>
+          <t>2881352</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5103099</t>
+          <t>5256792</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5103099</t>
+          <t>5256792</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5103099</t>
+          <t>5256792</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2B_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
+          <t>Población según si convive con personas que requieren dedicación o cuidados especiales en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
